--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -60,12 +60,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -433,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -469,6 +472,19 @@
       </c>
       <c r="C2" s="2" t="n"/>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -485,6 +485,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -511,6 +511,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,6 +524,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -550,6 +550,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -563,6 +563,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -602,6 +602,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -615,6 +615,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/duroc_machines.xlsx
+++ b/data/duroc_machines.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,6 +628,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>4395</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
